--- a/population-projection/src/main/resources/population_data/CSK-total-of-50-governships.xlsx
+++ b/population-projection/src/main/resources/population_data/CSK-total-of-50-governships.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\population-projection\src\main\resources\population_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257D5146-A115-4156-B193-5BD251B7A909}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7307F17-4CDF-4493-B6A6-86296318E1CE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="2" xr2:uid="{CA9327AE-032E-4159-9FEB-060911109237}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="4" xr2:uid="{CA9327AE-032E-4159-9FEB-060911109237}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="рождаемость 1867-1912" sheetId="3" r:id="rId3"/>
+    <sheet name="смертность 1867-1912" sheetId="4" r:id="rId4"/>
+    <sheet name="естественный прирост 1867-1912" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
   <si>
     <t>год</t>
   </si>
@@ -69,6 +71,24 @@
   </si>
   <si>
     <t>рождаемость</t>
+  </si>
+  <si>
+    <t>Поведение смертности населения 50 губерний Европейской части России по ЦСК</t>
+  </si>
+  <si>
+    <t>Поведение естественного прироста населения 50 губерний Европейской части России по ЦСК</t>
+  </si>
+  <si>
+    <t>смертность</t>
+  </si>
+  <si>
+    <t>Движение населения в 50 губерниях Европейской России за 1867-1912 гг. по ЦСК</t>
+  </si>
+  <si>
+    <t>естественный прирост</t>
+  </si>
+  <si>
+    <t>максимум обычных колебаний</t>
   </si>
 </sst>
 </file>
@@ -129,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -142,6 +162,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -194,7 +223,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="ru-RU"/>
-              <a:t>Поведение рождаемости населения 50 европейских губерний России</a:t>
+              <a:t>Рождаемость населения 50 европейских губерний России</a:t>
             </a:r>
             <a:br>
               <a:rPr lang="ru-RU"/>
@@ -222,6 +251,14 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11563644202804275"/>
+          <c:y val="1.0315924511259384E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -258,8 +295,662 @@
         <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'рождаемость 1867-1912'!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>среднее</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'рождаемость 1867-1912'!$A$4:$A$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>1867</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1868</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1869</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1871</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1872</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1873</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1874</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1875</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1876</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1877</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1878</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1879</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1881</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1882</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1883</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1884</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1885</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1886</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1887</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1888</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1889</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1890</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1891</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1892</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1893</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1894</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1895</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1912</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'рождаемость 1867-1912'!$C$4:$C$49</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>50.162499999999987</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D508-4F1A-98BE-27A694543C28}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'рождаемость 1867-1912'!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>минимум обычных колебаний</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'рождаемость 1867-1912'!$A$4:$A$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>1867</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1868</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1869</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1871</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1872</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1873</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1874</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1875</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1876</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1877</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1878</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1879</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1881</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1882</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1883</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1884</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1885</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1886</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1887</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1888</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1889</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1890</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1891</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1892</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1893</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1894</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1895</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1912</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'рождаемость 1867-1912'!$D$4:$D$49</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>48.6</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>48.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D508-4F1A-98BE-27A694543C28}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="0"/>
-          <c:order val="0"/>
+          <c:order val="2"/>
           <c:tx>
             <c:strRef>
               <c:f>'рождаемость 1867-1912'!$B$3</c:f>
@@ -593,660 +1284,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-D508-4F1A-98BE-27A694543C28}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'рождаемость 1867-1912'!$C$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>среднее</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="92D050"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'рождаемость 1867-1912'!$A$4:$A$49</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
-                <c:pt idx="0">
-                  <c:v>1867</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1868</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1869</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1870</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1871</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1872</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1873</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1874</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1875</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1876</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1877</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1878</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1879</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1880</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1881</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1882</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1883</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1884</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1885</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1886</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1887</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1888</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1889</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1890</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1891</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1892</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1893</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1894</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1895</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1896</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1897</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1898</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1899</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1900</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1901</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1902</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1903</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1904</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1905</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1906</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1907</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>1908</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1909</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1910</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1911</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1912</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'рождаемость 1867-1912'!$C$4:$C$49</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="46"/>
-                <c:pt idx="0">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>50.162499999999987</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D508-4F1A-98BE-27A694543C28}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'рождаемость 1867-1912'!$D$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>минимум обычных колебаний</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="FFC000"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'рождаемость 1867-1912'!$A$4:$A$49</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="46"/>
-                <c:pt idx="0">
-                  <c:v>1867</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1868</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1869</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1870</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1871</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1872</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1873</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1874</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1875</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1876</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1877</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1878</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1879</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1880</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1881</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1882</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1883</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1884</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1885</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1886</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1887</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1888</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1889</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1890</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1891</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1892</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1893</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1894</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1895</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1896</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1897</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1898</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1899</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1900</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1901</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1902</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1903</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1904</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1905</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1906</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1907</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>1908</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1909</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>1910</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>1911</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>1912</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'рождаемость 1867-1912'!$D$4:$D$49</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="46"/>
-                <c:pt idx="0">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>48.6</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>48.6</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-D508-4F1A-98BE-27A694543C28}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1462,6 +1499,2634 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1920" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Смертность населения 50 европейских губерний России</a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="ru-RU"/>
+            </a:br>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>в 186</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>7</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>-191</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>2</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t> годах (ЦСК)</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1920" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'смертность 1867-1912'!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>среднее</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="40000"/>
+                  <a:lumOff val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'смертность 1867-1912'!$A$4:$A$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>1867</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1868</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1869</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1871</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1872</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1873</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1874</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1875</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1876</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1877</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1878</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1879</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1881</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1882</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1883</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1884</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1885</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1886</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1887</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1888</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1889</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1890</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1891</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1892</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1893</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1894</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1895</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1912</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'смертность 1867-1912'!$C$4:$C$49</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>36.093333333333334</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6AB0-47B4-9C4F-F54C3F3DB6C2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'смертность 1867-1912'!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>минимум обычных колебаний</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'смертность 1867-1912'!$A$4:$A$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>1867</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1868</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1869</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1871</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1872</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1873</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1874</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1875</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1876</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1877</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1878</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1879</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1881</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1882</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1883</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1884</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1885</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1886</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1887</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1888</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1889</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1890</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1891</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1892</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1893</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1894</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1895</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1912</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'смертность 1867-1912'!$D$4:$D$49</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-6AB0-47B4-9C4F-F54C3F3DB6C2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'смертность 1867-1912'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>смертность</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'смертность 1867-1912'!$A$4:$A$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>1867</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1868</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1869</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1871</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1872</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1873</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1874</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1875</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1876</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1877</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1878</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1879</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1881</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1882</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1883</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1884</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1885</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1886</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1887</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1888</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1889</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1890</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1891</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1892</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1893</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1894</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1895</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1912</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'смертность 1867-1912'!$B$4:$B$49</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>36.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>39.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>38.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>37.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>41.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>35.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>34.6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>34.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>34.4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>38.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>34.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>36.1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>34.1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>40.4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>37.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>34.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>35.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>33.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>33.4</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>36.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>35.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>34.4</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>34.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>35.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>33.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31.7</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>31.2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>31.1</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>32.1</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>31.5</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>29.9</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>31.8</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>29.9</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>28.3</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>31.5</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>27.4</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>26.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6AB0-47B4-9C4F-F54C3F3DB6C2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="920032304"/>
+        <c:axId val="920033288"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="920032304"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="1865"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="920033288"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="920033288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="25"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="920032304"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1600" b="1" i="0" baseline="0"/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1920" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Естественный прирост населения 50 европейских губерний России</a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="ru-RU"/>
+            </a:br>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>в 186</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>7</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>-191</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>2</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t> годах (ЦСК)</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1920" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'естественный прирост 1867-1912'!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>среднее</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="31750" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="40000"/>
+                  <a:lumOff val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'естественный прирост 1867-1912'!$A$4:$A$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>1867</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1868</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1869</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1871</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1872</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1873</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1874</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1875</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1876</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1877</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1878</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1879</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1881</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1882</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1883</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1884</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1885</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1886</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1887</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1888</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1889</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1890</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1891</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1892</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1893</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1894</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1895</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1912</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'естественный прирост 1867-1912'!$E$4:$E$49</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>14.732000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5C58-4B64-9B03-29672459F231}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'естественный прирост 1867-1912'!$F$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>максимум обычных колебаний</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="31750" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="40000"/>
+                  <a:lumOff val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'естественный прирост 1867-1912'!$A$4:$A$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>1867</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1868</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1869</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1871</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1872</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1873</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1874</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1875</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1876</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1877</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1878</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1879</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1881</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1882</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1883</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1884</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1885</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1886</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1887</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1888</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1889</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1890</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1891</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1892</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1893</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1894</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1895</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1912</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'естественный прирост 1867-1912'!$F$4:$F$49</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5C58-4B64-9B03-29672459F231}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'естественный прирост 1867-1912'!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>естественный прирост</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'естественный прирост 1867-1912'!$A$4:$A$49</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>1867</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1868</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1869</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1871</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1872</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1873</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1874</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1875</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1876</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1877</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1878</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1879</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1881</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1882</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1883</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1884</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1885</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1886</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1887</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1888</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1889</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1890</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1891</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1892</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1893</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1894</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1895</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1897</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1898</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1899</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1901</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1902</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1903</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1904</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1905</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1906</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1907</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1908</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1909</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1910</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1911</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1912</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'естественный прирост 1867-1912'!$D$4:$D$49</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="46"/>
+                <c:pt idx="0">
+                  <c:v>14.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.0999999999999943</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.7999999999999972</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>15.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16.199999999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>15.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>15.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.0999999999999943</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>15.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13.600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>11.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>13.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>14.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>16.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>16.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>18.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>14.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>12.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>14.800000000000004</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>14.399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>14.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>14.600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>18.3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>15.399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>18.099999999999998</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>18.199999999999996</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>15.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>17.600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>18.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>18.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>13.099999999999998</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>17.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>18.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>16.400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>15.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>13.600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>17.600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>17.200000000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5C58-4B64-9B03-29672459F231}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="901785344"/>
+        <c:axId val="901786328"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="901785344"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="901786328"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="901786328"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="4"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="901785344"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1600" b="1" i="0" baseline="0"/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1502,7 +4167,1119 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2059,6 +5836,88 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5B32F34-09CE-4D0B-BA57-B2E35FF6D2DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DCC1997-F1D0-4793-AE56-F45B04267F89}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2620,7 +6479,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -4238,4 +8097,1958 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B97D27B-3BC1-48C7-B361-9677CB9E8AEE}">
+  <dimension ref="A1:D49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1867</v>
+      </c>
+      <c r="B4" s="1">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="C4" s="1">
+        <f>AVERAGE(B4:B33)</f>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D4" s="1">
+        <f>MIN(B4:B33)</f>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <f t="shared" ref="A5:A49" si="0">A4+1</f>
+        <v>1868</v>
+      </c>
+      <c r="B5" s="1">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="C5" s="1">
+        <f>C4</f>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D5" s="1">
+        <f>D4</f>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>1869</v>
+      </c>
+      <c r="B6" s="1">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" ref="C6:C49" si="1">C5</f>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" ref="D6:D49" si="2">D5</f>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>1870</v>
+      </c>
+      <c r="B7" s="1">
+        <v>35</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>1871</v>
+      </c>
+      <c r="B8" s="1">
+        <v>37.9</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>1872</v>
+      </c>
+      <c r="B9" s="1">
+        <v>41.2</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>1873</v>
+      </c>
+      <c r="B10" s="1">
+        <v>36.5</v>
+      </c>
+      <c r="C10" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D10" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>1874</v>
+      </c>
+      <c r="B11" s="1">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="C11" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D11" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>1875</v>
+      </c>
+      <c r="B12" s="1">
+        <v>34.6</v>
+      </c>
+      <c r="C12" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D12" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>1876</v>
+      </c>
+      <c r="B13" s="1">
+        <v>34.9</v>
+      </c>
+      <c r="C13" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D13" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>1877</v>
+      </c>
+      <c r="B14" s="1">
+        <v>34.4</v>
+      </c>
+      <c r="C14" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D14" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>1878</v>
+      </c>
+      <c r="B15" s="1">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="C15" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D15" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>1879</v>
+      </c>
+      <c r="B16" s="1">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="C16" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D16" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>1880</v>
+      </c>
+      <c r="B17" s="1">
+        <v>36.1</v>
+      </c>
+      <c r="C17" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D17" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>1881</v>
+      </c>
+      <c r="B18" s="1">
+        <v>34.1</v>
+      </c>
+      <c r="C18" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>1882</v>
+      </c>
+      <c r="B19" s="1">
+        <v>40.4</v>
+      </c>
+      <c r="C19" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>1883</v>
+      </c>
+      <c r="B20" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="C20" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>1884</v>
+      </c>
+      <c r="B21" s="1">
+        <v>34.5</v>
+      </c>
+      <c r="C21" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>1885</v>
+      </c>
+      <c r="B22" s="1">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="C22" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D22" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>1886</v>
+      </c>
+      <c r="B23" s="1">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="C23" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D23" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>1887</v>
+      </c>
+      <c r="B24" s="1">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="C24" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D24" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>1888</v>
+      </c>
+      <c r="B25" s="1">
+        <v>33.4</v>
+      </c>
+      <c r="C25" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D25" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>1889</v>
+      </c>
+      <c r="B26" s="1">
+        <v>35.5</v>
+      </c>
+      <c r="C26" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D26" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>1890</v>
+      </c>
+      <c r="B27" s="1">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="C27" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D27" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>1891</v>
+      </c>
+      <c r="B28" s="1">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="C28" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D28" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>1892</v>
+      </c>
+      <c r="B29" s="1">
+        <v>41</v>
+      </c>
+      <c r="C29" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D29" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>1893</v>
+      </c>
+      <c r="B30" s="1">
+        <v>34.4</v>
+      </c>
+      <c r="C30" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D30" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>1894</v>
+      </c>
+      <c r="B31" s="1">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="C31" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D31" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>1895</v>
+      </c>
+      <c r="B32" s="1">
+        <v>35.5</v>
+      </c>
+      <c r="C32" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D32" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>1896</v>
+      </c>
+      <c r="B33" s="1">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="C33" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D33" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>1897</v>
+      </c>
+      <c r="B34" s="1">
+        <v>31.7</v>
+      </c>
+      <c r="C34" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D34" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>1898</v>
+      </c>
+      <c r="B35" s="1">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="C35" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D35" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>1899</v>
+      </c>
+      <c r="B36" s="1">
+        <v>31.2</v>
+      </c>
+      <c r="C36" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D36" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>1900</v>
+      </c>
+      <c r="B37" s="1">
+        <v>31.1</v>
+      </c>
+      <c r="C37" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D37" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>1901</v>
+      </c>
+      <c r="B38" s="1">
+        <v>32.1</v>
+      </c>
+      <c r="C38" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D38" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>1902</v>
+      </c>
+      <c r="B39" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="C39" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D39" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>1903</v>
+      </c>
+      <c r="B40" s="1">
+        <v>30</v>
+      </c>
+      <c r="C40" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D40" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>1904</v>
+      </c>
+      <c r="B41" s="1">
+        <v>29.9</v>
+      </c>
+      <c r="C41" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D41" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>1905</v>
+      </c>
+      <c r="B42" s="1">
+        <v>31.8</v>
+      </c>
+      <c r="C42" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D42" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>1906</v>
+      </c>
+      <c r="B43" s="1">
+        <v>29.9</v>
+      </c>
+      <c r="C43" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D43" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>1907</v>
+      </c>
+      <c r="B44" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="C44" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D44" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>1908</v>
+      </c>
+      <c r="B45" s="1">
+        <v>28.3</v>
+      </c>
+      <c r="C45" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D45" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>1909</v>
+      </c>
+      <c r="B46" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="C46" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D46" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>1910</v>
+      </c>
+      <c r="B47" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="C47" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D47" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>1911</v>
+      </c>
+      <c r="B48" s="1">
+        <v>27.4</v>
+      </c>
+      <c r="C48" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D48" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>1912</v>
+      </c>
+      <c r="B49" s="1">
+        <v>26.5</v>
+      </c>
+      <c r="C49" s="1">
+        <f t="shared" si="1"/>
+        <v>36.093333333333334</v>
+      </c>
+      <c r="D49" s="1">
+        <f t="shared" si="2"/>
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A65ADA8-FB70-482D-B319-E181B0E49C3F}">
+  <dimension ref="A1:F49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1867</v>
+      </c>
+      <c r="B4" s="1">
+        <v>51.2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="D4" s="1">
+        <f>B4-C4</f>
+        <v>14.400000000000006</v>
+      </c>
+      <c r="E4" s="10">
+        <f>AVERAGE(D4,D6:D8,D10:D14,D16:D24,D26:D28,D30:D33)</f>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F4" s="10">
+        <f>MAX(D4,D6:D8,D10:D14,D16:D24,D26:D28,D30:D33)</f>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <f t="shared" ref="A5:A49" si="0">A4+1</f>
+        <v>1868</v>
+      </c>
+      <c r="B5" s="1">
+        <v>48.8</v>
+      </c>
+      <c r="C5" s="1">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" ref="D5:D49" si="1">B5-C5</f>
+        <v>9.0999999999999943</v>
+      </c>
+      <c r="E5" s="10">
+        <f>E4</f>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F5" s="10">
+        <f>F4</f>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>1869</v>
+      </c>
+      <c r="B6" s="1">
+        <v>49.7</v>
+      </c>
+      <c r="C6" s="1">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" si="1"/>
+        <v>11.400000000000006</v>
+      </c>
+      <c r="E6" s="10">
+        <f t="shared" ref="E6:E49" si="2">E5</f>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F6" s="10">
+        <f t="shared" ref="F6:F49" si="3">F5</f>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>1870</v>
+      </c>
+      <c r="B7" s="1">
+        <v>49.2</v>
+      </c>
+      <c r="C7" s="1">
+        <v>35</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="1"/>
+        <v>14.200000000000003</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F7" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>1871</v>
+      </c>
+      <c r="B8" s="1">
+        <v>51</v>
+      </c>
+      <c r="C8" s="1">
+        <v>37.9</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" si="1"/>
+        <v>13.100000000000001</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F8" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>1872</v>
+      </c>
+      <c r="B9" s="1">
+        <v>50</v>
+      </c>
+      <c r="C9" s="1">
+        <v>41.2</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="1"/>
+        <v>8.7999999999999972</v>
+      </c>
+      <c r="E9" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F9" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>1873</v>
+      </c>
+      <c r="B10" s="1">
+        <v>52.3</v>
+      </c>
+      <c r="C10" s="1">
+        <v>36.5</v>
+      </c>
+      <c r="D10" s="1">
+        <f t="shared" si="1"/>
+        <v>15.799999999999997</v>
+      </c>
+      <c r="E10" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F10" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>1874</v>
+      </c>
+      <c r="B11" s="1">
+        <v>51.4</v>
+      </c>
+      <c r="C11" s="1">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="D11" s="1">
+        <f t="shared" si="1"/>
+        <v>16.199999999999996</v>
+      </c>
+      <c r="E11" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F11" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>1875</v>
+      </c>
+      <c r="B12" s="1">
+        <v>51.5</v>
+      </c>
+      <c r="C12" s="1">
+        <v>34.6</v>
+      </c>
+      <c r="D12" s="1">
+        <f t="shared" si="1"/>
+        <v>16.899999999999999</v>
+      </c>
+      <c r="E12" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F12" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>1876</v>
+      </c>
+      <c r="B13" s="1">
+        <v>50.6</v>
+      </c>
+      <c r="C13" s="1">
+        <v>34.9</v>
+      </c>
+      <c r="D13" s="1">
+        <f t="shared" si="1"/>
+        <v>15.700000000000003</v>
+      </c>
+      <c r="E13" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F13" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>1877</v>
+      </c>
+      <c r="B14" s="1">
+        <v>49.6</v>
+      </c>
+      <c r="C14" s="1">
+        <v>34.4</v>
+      </c>
+      <c r="D14" s="1">
+        <f t="shared" si="1"/>
+        <v>15.200000000000003</v>
+      </c>
+      <c r="E14" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F14" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>1878</v>
+      </c>
+      <c r="B15" s="1">
+        <v>47.3</v>
+      </c>
+      <c r="C15" s="1">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="D15" s="1">
+        <f t="shared" si="1"/>
+        <v>9.0999999999999943</v>
+      </c>
+      <c r="E15" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F15" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>1879</v>
+      </c>
+      <c r="B16" s="1">
+        <v>50.2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="D16" s="1">
+        <f t="shared" si="1"/>
+        <v>15.400000000000006</v>
+      </c>
+      <c r="E16" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F16" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>1880</v>
+      </c>
+      <c r="B17" s="1">
+        <v>49.7</v>
+      </c>
+      <c r="C17" s="1">
+        <v>36.1</v>
+      </c>
+      <c r="D17" s="1">
+        <f t="shared" si="1"/>
+        <v>13.600000000000001</v>
+      </c>
+      <c r="E17" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F17" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>1881</v>
+      </c>
+      <c r="B18" s="1">
+        <v>49.1</v>
+      </c>
+      <c r="C18" s="1">
+        <v>34.1</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="E18" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F18" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>1882</v>
+      </c>
+      <c r="B19" s="1">
+        <v>51.6</v>
+      </c>
+      <c r="C19" s="1">
+        <v>40.4</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="1"/>
+        <v>11.200000000000003</v>
+      </c>
+      <c r="E19" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F19" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>1883</v>
+      </c>
+      <c r="B20" s="1">
+        <v>50.6</v>
+      </c>
+      <c r="C20" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" si="1"/>
+        <v>13.100000000000001</v>
+      </c>
+      <c r="E20" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F20" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>1884</v>
+      </c>
+      <c r="B21" s="1">
+        <v>51.5</v>
+      </c>
+      <c r="C21" s="1">
+        <v>34.5</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="E21" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F21" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>1885</v>
+      </c>
+      <c r="B22" s="1">
+        <v>50</v>
+      </c>
+      <c r="C22" s="1">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="D22" s="1">
+        <f t="shared" si="1"/>
+        <v>14.200000000000003</v>
+      </c>
+      <c r="E22" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F22" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>1886</v>
+      </c>
+      <c r="B23" s="1">
+        <v>49.5</v>
+      </c>
+      <c r="C23" s="1">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="D23" s="1">
+        <f t="shared" si="1"/>
+        <v>16.299999999999997</v>
+      </c>
+      <c r="E23" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F23" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>1887</v>
+      </c>
+      <c r="B24" s="1">
+        <v>49.9</v>
+      </c>
+      <c r="C24" s="1">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D24" s="1">
+        <f t="shared" si="1"/>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="E24" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F24" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>1888</v>
+      </c>
+      <c r="B25" s="1">
+        <v>51.6</v>
+      </c>
+      <c r="C25" s="1">
+        <v>33.4</v>
+      </c>
+      <c r="D25" s="1">
+        <f t="shared" si="1"/>
+        <v>18.200000000000003</v>
+      </c>
+      <c r="E25" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F25" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>1889</v>
+      </c>
+      <c r="B26" s="1">
+        <v>50.3</v>
+      </c>
+      <c r="C26" s="1">
+        <v>35.5</v>
+      </c>
+      <c r="D26" s="1">
+        <f t="shared" si="1"/>
+        <v>14.799999999999997</v>
+      </c>
+      <c r="E26" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F26" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>1890</v>
+      </c>
+      <c r="B27" s="1">
+        <v>49.6</v>
+      </c>
+      <c r="C27" s="1">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="D27" s="1">
+        <f t="shared" si="1"/>
+        <v>12.899999999999999</v>
+      </c>
+      <c r="E27" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F27" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>1891</v>
+      </c>
+      <c r="B28" s="1">
+        <v>50.6</v>
+      </c>
+      <c r="C28" s="1">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="D28" s="1">
+        <f t="shared" si="1"/>
+        <v>14.800000000000004</v>
+      </c>
+      <c r="E28" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F28" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>1892</v>
+      </c>
+      <c r="B29" s="1">
+        <v>46</v>
+      </c>
+      <c r="C29" s="1">
+        <v>41</v>
+      </c>
+      <c r="D29" s="1">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="E29" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F29" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>1893</v>
+      </c>
+      <c r="B30" s="1">
+        <v>48.8</v>
+      </c>
+      <c r="C30" s="1">
+        <v>34.4</v>
+      </c>
+      <c r="D30" s="1">
+        <f t="shared" si="1"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="E30" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F30" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>1894</v>
+      </c>
+      <c r="B31" s="1">
+        <v>49.2</v>
+      </c>
+      <c r="C31" s="1">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="D31" s="1">
+        <f t="shared" si="1"/>
+        <v>14.900000000000006</v>
+      </c>
+      <c r="E31" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F31" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>1895</v>
+      </c>
+      <c r="B32" s="1">
+        <v>50.1</v>
+      </c>
+      <c r="C32" s="1">
+        <v>35.5</v>
+      </c>
+      <c r="D32" s="1">
+        <f t="shared" si="1"/>
+        <v>14.600000000000001</v>
+      </c>
+      <c r="E32" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F32" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>1896</v>
+      </c>
+      <c r="B33" s="1">
+        <v>50.4</v>
+      </c>
+      <c r="C33" s="1">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="D33" s="1">
+        <f t="shared" si="1"/>
+        <v>17.100000000000001</v>
+      </c>
+      <c r="E33" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F33" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>1897</v>
+      </c>
+      <c r="B34" s="1">
+        <v>50</v>
+      </c>
+      <c r="C34" s="1">
+        <v>31.7</v>
+      </c>
+      <c r="D34" s="1">
+        <f t="shared" si="1"/>
+        <v>18.3</v>
+      </c>
+      <c r="E34" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F34" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>1898</v>
+      </c>
+      <c r="B35" s="1">
+        <v>48.6</v>
+      </c>
+      <c r="C35" s="1">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="D35" s="1">
+        <f t="shared" si="1"/>
+        <v>15.399999999999999</v>
+      </c>
+      <c r="E35" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F35" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>1899</v>
+      </c>
+      <c r="B36" s="1">
+        <v>49.3</v>
+      </c>
+      <c r="C36" s="1">
+        <v>31.2</v>
+      </c>
+      <c r="D36" s="1">
+        <f t="shared" si="1"/>
+        <v>18.099999999999998</v>
+      </c>
+      <c r="E36" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F36" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>1900</v>
+      </c>
+      <c r="B37" s="1">
+        <v>49.3</v>
+      </c>
+      <c r="C37" s="1">
+        <v>31.1</v>
+      </c>
+      <c r="D37" s="1">
+        <f t="shared" si="1"/>
+        <v>18.199999999999996</v>
+      </c>
+      <c r="E37" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F37" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>1901</v>
+      </c>
+      <c r="B38" s="1">
+        <v>47.9</v>
+      </c>
+      <c r="C38" s="1">
+        <v>32.1</v>
+      </c>
+      <c r="D38" s="1">
+        <f t="shared" si="1"/>
+        <v>15.799999999999997</v>
+      </c>
+      <c r="E38" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F38" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>1902</v>
+      </c>
+      <c r="B39" s="1">
+        <v>49.1</v>
+      </c>
+      <c r="C39" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="D39" s="1">
+        <f t="shared" si="1"/>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="E39" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F39" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>1903</v>
+      </c>
+      <c r="B40" s="1">
+        <v>48.1</v>
+      </c>
+      <c r="C40" s="1">
+        <v>30</v>
+      </c>
+      <c r="D40" s="1">
+        <f t="shared" si="1"/>
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E40" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F40" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>1904</v>
+      </c>
+      <c r="B41" s="1">
+        <v>48.6</v>
+      </c>
+      <c r="C41" s="1">
+        <v>29.9</v>
+      </c>
+      <c r="D41" s="1">
+        <f t="shared" si="1"/>
+        <v>18.700000000000003</v>
+      </c>
+      <c r="E41" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F41" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>1905</v>
+      </c>
+      <c r="B42" s="1">
+        <v>44.9</v>
+      </c>
+      <c r="C42" s="1">
+        <v>31.8</v>
+      </c>
+      <c r="D42" s="1">
+        <f t="shared" si="1"/>
+        <v>13.099999999999998</v>
+      </c>
+      <c r="E42" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F42" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>1906</v>
+      </c>
+      <c r="B43" s="1">
+        <v>47</v>
+      </c>
+      <c r="C43" s="1">
+        <v>29.9</v>
+      </c>
+      <c r="D43" s="1">
+        <f t="shared" si="1"/>
+        <v>17.100000000000001</v>
+      </c>
+      <c r="E43" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F43" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>1907</v>
+      </c>
+      <c r="B44" s="1">
+        <v>47.2</v>
+      </c>
+      <c r="C44" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="D44" s="1">
+        <f t="shared" si="1"/>
+        <v>18.700000000000003</v>
+      </c>
+      <c r="E44" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F44" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>1908</v>
+      </c>
+      <c r="B45" s="1">
+        <v>44.7</v>
+      </c>
+      <c r="C45" s="1">
+        <v>28.3</v>
+      </c>
+      <c r="D45" s="1">
+        <f t="shared" si="1"/>
+        <v>16.400000000000002</v>
+      </c>
+      <c r="E45" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F45" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>1909</v>
+      </c>
+      <c r="B46" s="1">
+        <v>44.7</v>
+      </c>
+      <c r="C46" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="D46" s="1">
+        <f t="shared" si="1"/>
+        <v>15.200000000000003</v>
+      </c>
+      <c r="E46" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F46" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>1910</v>
+      </c>
+      <c r="B47" s="1">
+        <v>45.1</v>
+      </c>
+      <c r="C47" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="D47" s="1">
+        <f t="shared" si="1"/>
+        <v>13.600000000000001</v>
+      </c>
+      <c r="E47" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F47" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>1911</v>
+      </c>
+      <c r="B48" s="1">
+        <v>45</v>
+      </c>
+      <c r="C48" s="1">
+        <v>27.4</v>
+      </c>
+      <c r="D48" s="1">
+        <f t="shared" si="1"/>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="E48" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F48" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>1912</v>
+      </c>
+      <c r="B49" s="1">
+        <v>43.7</v>
+      </c>
+      <c r="C49" s="1">
+        <v>26.5</v>
+      </c>
+      <c r="D49" s="1">
+        <f t="shared" si="1"/>
+        <v>17.200000000000003</v>
+      </c>
+      <c r="E49" s="10">
+        <f t="shared" si="2"/>
+        <v>14.732000000000003</v>
+      </c>
+      <c r="F49" s="10">
+        <f t="shared" si="3"/>
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>